--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdPlanNetInvestTrade002.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdPlanNetInvestTrade002.xlsx
@@ -1,16 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workSpaceZhu\tams-invest-parent\tams-invest-trade\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1155" windowWidth="12765" windowHeight="5385"/>
+    <workbookView xWindow="0" yWindow="1160" windowWidth="12770" windowHeight="5390"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>组合代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,11 +78,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资产二级类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资产三级类型</t>
+    <t>资产二级分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资产三级分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>确认日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -134,7 +142,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -146,12 +154,6 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,7 +427,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -433,27 +435,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="12.75" customWidth="1"/>
+    <col min="2" max="2" width="20.6328125" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="17.875" customWidth="1"/>
-    <col min="6" max="6" width="16.625" customWidth="1"/>
-    <col min="7" max="7" width="16.75" customWidth="1"/>
-    <col min="8" max="9" width="13.125" customWidth="1"/>
+    <col min="5" max="5" width="17.90625" customWidth="1"/>
+    <col min="6" max="6" width="16.6328125" customWidth="1"/>
+    <col min="7" max="7" width="16.7265625" customWidth="1"/>
+    <col min="8" max="9" width="13.08984375" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="26.625" customWidth="1"/>
-    <col min="12" max="12" width="29.125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="27.625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="12.875" customWidth="1"/>
-    <col min="15" max="15" width="57.25" customWidth="1"/>
-    <col min="16" max="16" width="23.75" customWidth="1"/>
+    <col min="11" max="12" width="26.6328125" customWidth="1"/>
+    <col min="13" max="13" width="29.08984375" style="3" customWidth="1"/>
+    <col min="14" max="14" width="27.6328125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="12.90625" customWidth="1"/>
+    <col min="16" max="16" width="57.26953125" customWidth="1"/>
+    <col min="17" max="17" width="23.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -487,22 +489,21 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
